--- a/Documentation/LCC-Pico-Stepper_v2_7.xlsx
+++ b/Documentation/LCC-Pico-Stepper_v2_7.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GdriveBG\KiCad\LCC-Pico-Node_v2_7\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Attic\Documents\GitHub\LCC-Pico-Node\LCC-RPi-Pico-Board\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{06F4AA26-7A9D-468D-A005-53AB36BA2DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F79B4918-F6A3-40B9-A904-0586D1E70345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8475" yWindow="285" windowWidth="27555" windowHeight="15345" xr2:uid="{367CDB51-5C52-45D8-B9E9-34FFAB20A32F}"/>
+    <workbookView xWindow="2055" yWindow="690" windowWidth="23265" windowHeight="19695" xr2:uid="{367CDB51-5C52-45D8-B9E9-34FFAB20A32F}"/>
   </bookViews>
   <sheets>
     <sheet name="LCC-Pico-Stepper_v2_7" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="193">
   <si>
     <t>Reference</t>
   </si>
@@ -37,12 +37,6 @@
     <t>Qty</t>
   </si>
   <si>
-    <t>C1,C3</t>
-  </si>
-  <si>
-    <t>0.1uF</t>
-  </si>
-  <si>
     <t>~</t>
   </si>
   <si>
@@ -64,12 +58,6 @@
     <t>22uF</t>
   </si>
   <si>
-    <t>C6,C15,C19,C20</t>
-  </si>
-  <si>
-    <t>100nF</t>
-  </si>
-  <si>
     <t>C7</t>
   </si>
   <si>
@@ -464,6 +452,153 @@
   </si>
   <si>
     <t>SamacSys_Parts:ABM3</t>
+  </si>
+  <si>
+    <t>C1,C3,C6,C15,C19,C20</t>
+  </si>
+  <si>
+    <t>0.1uF, 100nF</t>
+  </si>
+  <si>
+    <t>C1206C104K3RAC7411</t>
+  </si>
+  <si>
+    <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT 25V 0.1uF X7R 1206 10%</t>
+  </si>
+  <si>
+    <t>REF1016471M035K</t>
+  </si>
+  <si>
+    <t>Aluminum Electrolytic Capacitors - Radial Leaded Radial Leaded Aluminum Electrolytic Capacitor</t>
+  </si>
+  <si>
+    <t>CL31A226MOCLNNC</t>
+  </si>
+  <si>
+    <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT 22uF+/-20% 16V X5R 3 1206</t>
+  </si>
+  <si>
+    <t>CL31B105KAHNFNE</t>
+  </si>
+  <si>
+    <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT 1uF+/-10% 25V X7R 32 1206</t>
+  </si>
+  <si>
+    <t>C1206C220J3HACTU</t>
+  </si>
+  <si>
+    <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT 25V 22pF X8R 1206 5%</t>
+  </si>
+  <si>
+    <t>CL31B475KOHNFNE</t>
+  </si>
+  <si>
+    <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT 4.7uF+/-10% 16V X7R 1206</t>
+  </si>
+  <si>
+    <t>Rectifiers Diode, SMA, 1000V, 1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resettable Fuses - PPTC </t>
+  </si>
+  <si>
+    <t>Switching Voltage Regulators 4.5-18Vin Dual 2A Ou t Sync SD Cnvrtr A A 595-TPS54294PWP</t>
+  </si>
+  <si>
+    <t>MCP2518FDT-E/SL</t>
+  </si>
+  <si>
+    <t>CAN Interface IC Stand-alone Low Power CAN FD Controller w/SPI Interface Grade1</t>
+  </si>
+  <si>
+    <t>CAN Interface IC CAN Flexible Data Rate Transceiver</t>
+  </si>
+  <si>
+    <t>BR24G512F-3AGTE2</t>
+  </si>
+  <si>
+    <t>EEPROM I2C BUS(2-Wre) 512K SOP8 EEPROM</t>
+  </si>
+  <si>
+    <t>MTJ-880X1</t>
+  </si>
+  <si>
+    <t>Modular Connectors / Ethernet Connectors 8P8C TYPE 0 GLD FLSH BLK</t>
+  </si>
+  <si>
+    <t>Power Inductors - SMD Ind,3.2x2.5x1mm,2.2uH+/-20%,4A,shd AEC-Q200</t>
+  </si>
+  <si>
+    <t>Power Inductors - SMD Ind,3.2x2.5x1mm,3.3uH+/-20%,3.1A,shd AEC-Q200</t>
+  </si>
+  <si>
+    <t>MOSFETs P-Ch ENH FET -20V 52mOh -5A</t>
+  </si>
+  <si>
+    <t>ERA-8AEB1243V</t>
+  </si>
+  <si>
+    <t>Thin Film Resistors - SMD 1206 124Kohm 25ppm 0.1% AEC-Q200</t>
+  </si>
+  <si>
+    <t>ERA-8AEB2212V</t>
+  </si>
+  <si>
+    <t>Thin Film Resistors - SMD 1206 22.1Kohm 25ppm 0.1% AEC-Q200</t>
+  </si>
+  <si>
+    <t>ERA-8AEB7322V</t>
+  </si>
+  <si>
+    <t>Thin Film Resistors - SMD 1206 73.2Kohm 25ppm 0.1% AEC-Q200</t>
+  </si>
+  <si>
+    <t>RT1206FRE07820RL</t>
+  </si>
+  <si>
+    <t>Thin Film Resistors - SMD 1/4W 820 ohm 1% 50ppm</t>
+  </si>
+  <si>
+    <t>RT1206FRE07560RL</t>
+  </si>
+  <si>
+    <t>Thin Film Resistors - SMD 560   OHM   1%  50PPM   1/4W</t>
+  </si>
+  <si>
+    <t>RT1206FRE072KL</t>
+  </si>
+  <si>
+    <t>Thin Film Resistors - SMD 1/4W 2K ohm 1% 50ppm</t>
+  </si>
+  <si>
+    <t>RT1206DRD076K8L</t>
+  </si>
+  <si>
+    <t>Thin Film Resistors - SMD 6.8 kOhms 250 mW 0.5 % 1206</t>
+  </si>
+  <si>
+    <t>TS11-674-43-BK-160-RA-D</t>
+  </si>
+  <si>
+    <t>Tactile Switches 6 x 7.4 mm 4.3 mm 160 gf Black Right Angle Through Hole SPST</t>
+  </si>
+  <si>
+    <t>ABM3-40.000MHZ-B2-T</t>
+  </si>
+  <si>
+    <t>Crystals Xtal 5032 2-SMD 40MHz Tol +/-20ppm Stab +/-50ppm -20C - 70C 18pF 25 Ohms</t>
+  </si>
+  <si>
+    <t>156120VS75000</t>
+  </si>
+  <si>
+    <t>Single Color LEDs WL-SMRW SMD RvMt Mon Wtrclr Rect 1206BtGn</t>
+  </si>
+  <si>
+    <t>Mfr. #</t>
+  </si>
+  <si>
+    <t>Description</t>
   </si>
 </sst>
 </file>
@@ -1310,875 +1445,1039 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
-    <col min="2" max="2" width="30.5703125" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="66.7109375" customWidth="1"/>
-    <col min="5" max="5" width="26.85546875" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="4" width="30.5703125" customWidth="1"/>
+    <col min="5" max="5" width="60.5703125" customWidth="1"/>
+    <col min="6" max="6" width="66.7109375" customWidth="1"/>
+    <col min="7" max="7" width="26.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
       <c r="D1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>7</v>
       </c>
       <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>150</v>
+      </c>
+      <c r="E4" t="s">
+        <v>151</v>
+      </c>
+      <c r="F4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="D5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>156</v>
+      </c>
+      <c r="E7" t="s">
+        <v>157</v>
+      </c>
+      <c r="F7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>189</v>
+      </c>
+      <c r="E9" t="s">
+        <v>190</v>
+      </c>
+      <c r="F9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>1</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>2</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>1</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>1</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>6</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
       </c>
       <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" t="s">
+        <v>158</v>
+      </c>
+      <c r="F10" t="s">
         <v>25</v>
       </c>
-      <c r="D10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B11" t="s">
         <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>189</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="F11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
       <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" t="s">
+        <v>159</v>
+      </c>
+      <c r="F12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" t="s">
         <v>30</v>
       </c>
-      <c r="C12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
+        <v>1</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" t="s">
+        <v>160</v>
+      </c>
+      <c r="F13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>1</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" t="s">
+        <v>161</v>
+      </c>
+      <c r="E14" t="s">
+        <v>162</v>
+      </c>
+      <c r="F14" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>1</v>
+      </c>
+      <c r="B15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" t="s">
+        <v>163</v>
+      </c>
+      <c r="F15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>1</v>
+      </c>
+      <c r="B17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" t="s">
+        <v>164</v>
+      </c>
+      <c r="E17" t="s">
+        <v>165</v>
+      </c>
+      <c r="F17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>2</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>1</v>
-      </c>
-      <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>1</v>
-      </c>
-      <c r="B15" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>1</v>
-      </c>
-      <c r="B16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>1</v>
-      </c>
-      <c r="B17" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>1</v>
       </c>
       <c r="B18" t="s">
         <v>52</v>
       </c>
       <c r="C18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" t="s">
+        <v>166</v>
+      </c>
+      <c r="E18" t="s">
+        <v>167</v>
+      </c>
+      <c r="F18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18" t="s">
         <v>53</v>
       </c>
-      <c r="D18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
+        <v>1</v>
+      </c>
+      <c r="B19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" t="s">
+        <v>97</v>
+      </c>
+      <c r="E19" t="s">
+        <v>168</v>
+      </c>
+      <c r="F19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>1</v>
+      </c>
+      <c r="B20" t="s">
+        <v>101</v>
+      </c>
+      <c r="C20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" t="s">
+        <v>101</v>
+      </c>
+      <c r="E20" t="s">
+        <v>169</v>
+      </c>
+      <c r="F20" t="s">
+        <v>99</v>
+      </c>
+      <c r="G20" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>1</v>
+      </c>
+      <c r="B21" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" t="s">
+        <v>103</v>
+      </c>
+      <c r="E21" t="s">
+        <v>170</v>
+      </c>
+      <c r="F21" t="s">
+        <v>105</v>
+      </c>
+      <c r="G21" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>1</v>
+      </c>
+      <c r="B22" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D22" t="s">
+        <v>171</v>
+      </c>
+      <c r="E22" t="s">
+        <v>172</v>
+      </c>
+      <c r="F22" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
         <v>2</v>
       </c>
-      <c r="B19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" t="s">
-        <v>58</v>
-      </c>
-      <c r="E19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>2</v>
-      </c>
-      <c r="B20" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" t="s">
-        <v>61</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>1</v>
-      </c>
-      <c r="B21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" t="s">
-        <v>63</v>
-      </c>
-      <c r="D21" t="s">
-        <v>64</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+      <c r="B23" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23" t="s">
+        <v>173</v>
+      </c>
+      <c r="E23" t="s">
+        <v>174</v>
+      </c>
+      <c r="F23" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>1</v>
+      </c>
+      <c r="B24" t="s">
+        <v>112</v>
+      </c>
+      <c r="C24" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" t="s">
+        <v>175</v>
+      </c>
+      <c r="E24" t="s">
+        <v>176</v>
+      </c>
+      <c r="F24" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
         <v>3</v>
       </c>
-      <c r="B22" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" t="s">
-        <v>66</v>
-      </c>
-      <c r="D22" t="s">
-        <v>67</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>1</v>
-      </c>
-      <c r="B23" t="s">
-        <v>68</v>
-      </c>
-      <c r="C23" t="s">
-        <v>69</v>
-      </c>
-      <c r="D23" t="s">
-        <v>70</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>1</v>
-      </c>
-      <c r="B24" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" t="s">
-        <v>72</v>
-      </c>
-      <c r="D24" t="s">
-        <v>73</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>2</v>
-      </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
-      </c>
-      <c r="D25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+      <c r="F25" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="D26" t="s">
-        <v>79</v>
+        <v>177</v>
       </c>
       <c r="E26" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+      <c r="F26" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="C27" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="D27" t="s">
-        <v>79</v>
+        <v>179</v>
       </c>
       <c r="E27" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+      <c r="F27" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="C28" t="s">
-        <v>83</v>
-      </c>
-      <c r="D28" t="s">
-        <v>84</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+      <c r="F28" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="C29" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="D29" t="s">
-        <v>87</v>
+        <v>181</v>
       </c>
       <c r="E29" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+      <c r="F29" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="C30" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="D30" t="s">
-        <v>87</v>
+        <v>183</v>
       </c>
       <c r="E30" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+      <c r="F30" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
-      </c>
-      <c r="D31" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+      <c r="F31" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>1</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="C32" t="s">
-        <v>93</v>
-      </c>
-      <c r="D32" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+      <c r="F32" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="C33" t="s">
-        <v>95</v>
-      </c>
-      <c r="D33" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+      <c r="F33" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="C34" t="s">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="D34" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+      <c r="E34" t="s">
+        <v>186</v>
+      </c>
+      <c r="F34" t="s">
+        <v>135</v>
+      </c>
+      <c r="G34" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>1</v>
       </c>
       <c r="B35" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C35" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="D35" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+      <c r="E35" t="s">
+        <v>186</v>
+      </c>
+      <c r="F35" t="s">
+        <v>135</v>
+      </c>
+      <c r="G35" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>1</v>
       </c>
       <c r="B36" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="C36" t="s">
-        <v>101</v>
+        <v>138</v>
       </c>
       <c r="D36" t="s">
-        <v>103</v>
+        <v>185</v>
       </c>
       <c r="E36" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+      <c r="F36" t="s">
+        <v>135</v>
+      </c>
+      <c r="G36" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>1</v>
       </c>
       <c r="B37" t="s">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="C37" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="D37" t="s">
-        <v>103</v>
+        <v>187</v>
       </c>
       <c r="E37" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
-        <v>1</v>
-      </c>
-      <c r="B38" t="s">
-        <v>106</v>
-      </c>
-      <c r="C38" t="s">
-        <v>107</v>
-      </c>
-      <c r="D38" t="s">
-        <v>109</v>
-      </c>
-      <c r="E38" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
-        <v>1</v>
-      </c>
-      <c r="B39" t="s">
-        <v>110</v>
-      </c>
-      <c r="C39" t="s">
-        <v>111</v>
-      </c>
-      <c r="D39" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+      <c r="F37" t="s">
+        <v>143</v>
+      </c>
+      <c r="G37" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>2</v>
       </c>
       <c r="B40" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
       <c r="C40" t="s">
-        <v>114</v>
-      </c>
-      <c r="D40" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="F40" t="s">
+        <v>57</v>
+      </c>
+      <c r="G40" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>115</v>
+        <v>59</v>
       </c>
       <c r="C41" t="s">
-        <v>116</v>
-      </c>
-      <c r="D41" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+      <c r="F41" t="s">
+        <v>60</v>
+      </c>
+      <c r="G41" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>117</v>
+        <v>62</v>
       </c>
       <c r="C42" t="s">
-        <v>118</v>
-      </c>
-      <c r="D42" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="F42" t="s">
+        <v>63</v>
+      </c>
+      <c r="G42" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>119</v>
+        <v>65</v>
       </c>
       <c r="C43" t="s">
-        <v>120</v>
-      </c>
-      <c r="D43" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="F43" t="s">
+        <v>66</v>
+      </c>
+      <c r="G43" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B44" t="s">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="C44" t="s">
-        <v>122</v>
-      </c>
-      <c r="D44" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+      <c r="F44" t="s">
+        <v>69</v>
+      </c>
+      <c r="G44" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B45" t="s">
-        <v>123</v>
+        <v>71</v>
       </c>
       <c r="C45" t="s">
-        <v>124</v>
-      </c>
-      <c r="D45" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="F45" t="s">
+        <v>72</v>
+      </c>
+      <c r="G45" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>1</v>
       </c>
       <c r="B46" t="s">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="C46" t="s">
-        <v>126</v>
-      </c>
-      <c r="D46" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="F46" t="s">
+        <v>75</v>
+      </c>
+      <c r="G46" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>1</v>
       </c>
       <c r="B47" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="C47" t="s">
-        <v>128</v>
-      </c>
-      <c r="D47" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F47" t="s">
+        <v>75</v>
+      </c>
+      <c r="G47" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>1</v>
       </c>
       <c r="B48" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="C48" t="s">
-        <v>130</v>
-      </c>
-      <c r="D48" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="F48" t="s">
+        <v>80</v>
+      </c>
+      <c r="G48" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>1</v>
       </c>
       <c r="B49" t="s">
-        <v>131</v>
+        <v>82</v>
       </c>
       <c r="C49" t="s">
-        <v>132</v>
-      </c>
-      <c r="D49" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+      <c r="F49" t="s">
+        <v>83</v>
+      </c>
+      <c r="G49" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>1</v>
       </c>
       <c r="B50" t="s">
-        <v>133</v>
+        <v>85</v>
       </c>
       <c r="C50" t="s">
-        <v>134</v>
-      </c>
-      <c r="D50" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+      <c r="F50" t="s">
+        <v>83</v>
+      </c>
+      <c r="G50" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>1</v>
       </c>
       <c r="B51" t="s">
-        <v>136</v>
+        <v>87</v>
       </c>
       <c r="C51" t="s">
-        <v>137</v>
-      </c>
-      <c r="D51" t="s">
-        <v>139</v>
-      </c>
-      <c r="E51" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+      <c r="F51" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>1</v>
       </c>
       <c r="B52" t="s">
-        <v>140</v>
+        <v>89</v>
       </c>
       <c r="C52" t="s">
-        <v>141</v>
-      </c>
-      <c r="D52" t="s">
-        <v>139</v>
-      </c>
-      <c r="E52" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+      <c r="F52" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>1</v>
       </c>
       <c r="B53" t="s">
-        <v>142</v>
+        <v>91</v>
       </c>
       <c r="C53" t="s">
-        <v>143</v>
-      </c>
-      <c r="D53" t="s">
-        <v>139</v>
-      </c>
-      <c r="E53" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="F53" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>1</v>
       </c>
       <c r="B54" t="s">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="C54" t="s">
-        <v>145</v>
-      </c>
-      <c r="D54" t="s">
-        <v>147</v>
-      </c>
-      <c r="E54" t="s">
-        <v>146</v>
+        <v>92</v>
+      </c>
+      <c r="F54" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>1</v>
+      </c>
+      <c r="B55" t="s">
+        <v>95</v>
+      </c>
+      <c r="C55" t="s">
+        <v>94</v>
+      </c>
+      <c r="F55" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
